--- a/output/pdf_financials_xlsx/INTG.xlsx
+++ b/output/pdf_financials_xlsx/INTG.xlsx
@@ -1931,10 +1931,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.577008</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.527726</v>
       </c>
     </row>
     <row r="93">
@@ -2338,10 +2338,10 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>1</v>
+        <v>0.823931</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-2.662942</v>
       </c>
     </row>
     <row r="119">
@@ -3160,7 +3160,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -3499,7 +3503,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -4053,7 +4061,11 @@
           <t>Exploration and evaluation expenditures 5</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -4780,7 +4792,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/INTG.xlsx
+++ b/output/pdf_financials_xlsx/INTG.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.826019</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.322499</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.387794</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.826019</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.322499</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.387794</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.826019</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.352499</v>
+        <v>0.03</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.411467</v>
+        <v>0.023673</v>
       </c>
     </row>
     <row r="49">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/INTG.xlsx
+++ b/output/pdf_financials_xlsx/INTG.xlsx
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.010968</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.075574</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.211455</v>
       </c>
     </row>
     <row r="102">
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.123551</v>
+        <v>-0.134519</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.134967</v>
+        <v>0.059393</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.07133200000000001</v>
+        <v>-0.140123</v>
       </c>
     </row>
     <row r="107">
@@ -2213,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.120583</v>
       </c>
     </row>
     <row r="111">
@@ -3594,7 +3594,11 @@
           <t>Accretion expense 7</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -3879,7 +3883,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>-0.010968</v>
       </c>
@@ -4895,7 +4903,11 @@
           <t>Proceeds from shares issued 7</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
         <v>1</v>
       </c>
